--- a/docs/decision-matrix.xlsx
+++ b/docs/decision-matrix.xlsx
@@ -11,9 +11,11 @@
     <sheet name="Legend" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Voltage" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Amperage" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Protocol" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Control" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="EMI Hardening" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Motor" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Shaft Sensor" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Protocol" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Control" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="EMI Hardening" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -59,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="223">
   <si>
     <t xml:space="preserve">Open-Secure-ESC — Design Option Decision Matrix</t>
   </si>
@@ -139,6 +141,21 @@
     <t xml:space="preserve">The 4 EMI tiers: governing standard(s) and BOM part (or layout-only) per tier.</t>
   </si>
   <si>
+    <t xml:space="preserve">Motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brushed vs brushless: bridge topology, switch-position count, gate-driver part, shunt count. Changes the power stage, not just a setting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaft Sensor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensorless / Hall / quadrature encoder / resolver: MCU pin budget, connector, and any added IC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amended 2026-08-16: added the Motor and Shaft Sensor axis sheets. Cells reading 'TBD -- requires primary-source verification' are genuinely unsourced, not placeholders to be filled in from memory (AGENTS.md Sec.1.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Voltage Tier Decision Matrix</t>
   </si>
   <si>
@@ -277,6 +294,180 @@
     <t xml:space="preserve">Shunt part: Vishay WSLP2512 [23] (3.0W package rating). "Shunt Qty Needed" = ROUNDUP(Shunt Power / 3W, 0); at 80A/120A this correctly computes 2x and 3x devices in parallel (7.2W / 3 tiers exceeds a single package's rating). FET parallel count and gate-driver reuse are a BOM-commonality choice (AGENTS.md §4 judgment call), not a datasheet requirement -- a smaller SO-8 FET would be leaner for the 10A-30A tiers if part-count commonality were not prioritized.</t>
   </si>
   <si>
+    <t xml:space="preserve">Motor Type Decision Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build axis: Motor (Brushed / Brushless)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridge Topology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch Positions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Output Terminals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shunt Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commutation Requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brushless (BLDC / PMSM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three half-bridges (3-phase inverter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (3 high + 3 low)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TI DRV8353S, 3-phase smart gate driver, SPI variant [21]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (PH_A / PH_B / PH_C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (one per phase, low-side)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Six-step trapezoidal or FOC; rotor position from the Shaft Sensor axis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[21]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brushed (DC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single H-bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (2 high + 2 low)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD -- requires primary-source verification (AGENTS.md Sec.1.3). No H-bridge gate driver has been sourced or verified in this repo. NOTE, not yet vetted: a 3-phase driver such as the DRV8353S [21] can drive an H-bridge by using two of its three half-bridges and leaving the third unused -- this reuses an already-verified part at the cost of wasted silicon and board area, and must be checked against [21] before adoption.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (M+ / M-)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-2 (bridge-leg or in-line)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None -- direction and magnitude set by bridge polarity and duty cycle; no rotor position needed for basic operation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaft Sensor Decision Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build axis: Shaft Sensor (None-sensorless / Hall / Quadrature encoder / Resolver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensor Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rotor Position Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCU Pins Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional BOM Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firmware Workflow Steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None (sensorless)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Back-EMF / observer computed from phase voltages and currents; same observer the Control sheet's closed-loop rows already use (TI SLAAE96A [13])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 ADC (one per phase voltage divider). Reuses the current-sense ADC channels already allocated on the Amperage axis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 resistor dividers (6 R) plus filter capacitors, one per phase. Generic passives, values sized against the pack voltage of the chosen Voltage tier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None -- no sensor cable leaves the board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement the observer per [13]; handle open-loop startup ramp, since back-EMF is unusable near zero speed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[13]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hall effect (3-sensor, 120 deg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three digital Hall outputs giving six commutation states per electrical revolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 digital in (interrupt-capable), plus a sensor supply rail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 pull-up resistors plus ESD protection on the cable entry. Sensor part: TI DRV5013 is carried from the Control sheet as a fallback candidate, at that sheet's existing status -- it has not been separately verified for this axis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-pin (VCC, GND, HA, HB, HC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decode the 3-bit Hall state into a 6-step commutation table; derive speed from state-transition timing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quadrature encoder (incremental)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two phase-quadrature channels A/B, plus optional once-per-rev index Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 digital in, or 3 with index. Prefer a timer with a hardware quadrature decoder if the chosen MCU has one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pull-ups for an open-collector encoder, or a differential line receiver for RS-422 encoders -- TBD -- requires primary-source verification (AGENTS.md Sec.1.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-pin (VCC, GND, A, B) or 6-pin with Z and shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configure the hardware quadrature decoder; establish a zero reference from the index pulse or a homing routine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratiometric SIN/COS windings excited by an AC reference; absolute position within one electrical revolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depends on the converter: an SPI or parallel bus to a resolver-to-digital converter, plus an excitation output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolver-to-digital converter IC and an excitation amplifier -- TBD -- requires primary-source verification (AGENTS.md Sec.1.3). This is the only shaft-sensor option that adds a whole IC to the BOM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-pin (EXC+, EXC-, SIN+, SIN-, COS+, COS-), shielded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive the excitation reference; read absolute angle from the converter; no startup ramp needed, unlike sensorless.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Protocol Interface Decision Matrix</t>
   </si>
   <si>
@@ -286,9 +477,6 @@
     <t xml:space="preserve">MCU Native Peripheral?</t>
   </si>
   <si>
-    <t xml:space="preserve">Additional BOM Component</t>
-  </si>
-  <si>
     <t xml:space="preserve">Workflow Steps</t>
   </si>
   <si>
@@ -304,9 +492,6 @@
     <t xml:space="preserve">Configure MCU timer capture/compare input; map duty-cycle/period per protocol variant.</t>
   </si>
   <si>
-    <t xml:space="preserve">[1]</t>
-  </si>
-  <si>
     <t xml:space="preserve">SBus</t>
   </si>
   <si>
@@ -445,9 +630,6 @@
     <t xml:space="preserve">Feedback Method</t>
   </si>
   <si>
-    <t xml:space="preserve">Firmware Workflow Steps</t>
-  </si>
-  <si>
     <t xml:space="preserve">Open-loop</t>
   </si>
   <si>
@@ -455,9 +637,6 @@
   </si>
   <si>
     <t xml:space="preserve">Map input protocol command directly to PWM duty cycle; no observer or control-law firmware needed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
   </si>
   <si>
     <t xml:space="preserve">Closed-loop differential</t>
@@ -557,16 +736,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0&quot; V&quot;"/>
-    <numFmt numFmtId="166" formatCode="General"/>
-    <numFmt numFmtId="167" formatCode="0.00\x"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="0.00\x"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.00"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -628,6 +806,19 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -658,6 +849,21 @@
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -749,8 +955,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -758,11 +968,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -790,7 +1000,19 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -798,11 +1020,11 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -810,7 +1032,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -818,11 +1040,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -830,20 +1056,24 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1098,177 +1328,198 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" customFormat="false" ht="285.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -1302,267 +1553,267 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="A1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="12" t="n">
+      <c r="A2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="16" t="n">
         <v>3.6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="12" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="16" t="n">
         <v>4.2</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="12" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="16" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="13" t="s">
+      <c r="A10" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="B10" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="C10" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="D10" s="17" t="s">
         <v>42</v>
       </c>
+      <c r="E10" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="14" t="n">
+      <c r="A11" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="19" t="n">
         <f aca="false">$B$6*B11</f>
         <v>7.2</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="19" t="n">
         <f aca="false">$B$7*B11</f>
         <v>8.4</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="19" t="n">
         <f aca="false">$B$8*B11</f>
         <v>5</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="6" t="s">
+      <c r="F11" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="14" t="n">
+      <c r="A12" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="19" t="n">
         <f aca="false">$B$6*B12</f>
         <v>14.4</v>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="19" t="n">
         <f aca="false">$B$7*B12</f>
         <v>16.8</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="19" t="n">
         <f aca="false">$B$8*B12</f>
         <v>10</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="6" t="s">
+      <c r="F12" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="14" t="n">
+      <c r="A13" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="19" t="n">
         <f aca="false">$B$6*B13</f>
         <v>21.6</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="19" t="n">
         <f aca="false">$B$7*B13</f>
         <v>25.2</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="19" t="n">
         <f aca="false">$B$8*B13</f>
         <v>15</v>
       </c>
-      <c r="F13" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="6" t="s">
+      <c r="F13" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="14" t="n">
+      <c r="A14" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="19" t="n">
         <f aca="false">$B$6*B14</f>
         <v>28.8</v>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="19" t="n">
         <f aca="false">$B$7*B14</f>
         <v>33.6</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="19" t="n">
         <f aca="false">$B$8*B14</f>
         <v>20</v>
       </c>
-      <c r="F14" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" s="6" t="s">
+      <c r="F14" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="14" t="n">
+      <c r="A15" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="19" t="n">
         <f aca="false">$B$6*B15</f>
         <v>43.2</v>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="19" t="n">
         <f aca="false">$B$7*B15</f>
         <v>50.4</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="19" t="n">
         <f aca="false">$B$8*B15</f>
         <v>30</v>
       </c>
-      <c r="F15" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" s="6" t="s">
+      <c r="F15" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1588,433 +1839,433 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="A1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
+      <c r="A2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="13" t="s">
+      <c r="A4" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="B4" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="C4" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="D4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="E4" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="F4" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="L4" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>42</v>
+      <c r="G4" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="18" t="n">
+      <c r="C5" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="22" t="n">
         <f aca="false">B5*120</f>
         <v>120</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="23" t="n">
         <f aca="false">D5/A5</f>
         <v>12</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="20" t="n">
+      <c r="F5" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="H5" s="21" t="n">
+      <c r="H5" s="25" t="n">
         <f aca="false">A5*G5</f>
         <v>100</v>
       </c>
-      <c r="I5" s="22" t="n">
+      <c r="I5" s="26" t="n">
         <f aca="false">A5^2*(G5/1000)</f>
         <v>1</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="22" t="n">
         <f aca="false">ROUNDUP(I5/3,0)</f>
         <v>1</v>
       </c>
-      <c r="K5" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="L5" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="M5" s="6" t="s">
+      <c r="K5" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="18" t="n">
+      <c r="C6" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="22" t="n">
         <f aca="false">B6*120</f>
         <v>120</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="23" t="n">
         <f aca="false">D6/A6</f>
         <v>6</v>
       </c>
-      <c r="F6" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="20" t="n">
+      <c r="F6" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="21" t="n">
+      <c r="H6" s="25" t="n">
         <f aca="false">A6*G6</f>
         <v>100</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="26" t="n">
         <f aca="false">A6^2*(G6/1000)</f>
         <v>2</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="22" t="n">
         <f aca="false">ROUNDUP(I6/3,0)</f>
         <v>1</v>
       </c>
-      <c r="K6" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="L6" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="M6" s="6" t="s">
+      <c r="K6" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M6" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="18" t="n">
+      <c r="C7" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="22" t="n">
         <f aca="false">B7*120</f>
         <v>120</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="23" t="n">
         <f aca="false">D7/A7</f>
         <v>4</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7" s="20" t="n">
+      <c r="F7" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="21" t="n">
+      <c r="H7" s="25" t="n">
         <f aca="false">A7*G7</f>
         <v>60</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="26" t="n">
         <f aca="false">A7^2*(G7/1000)</f>
         <v>1.8</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="22" t="n">
         <f aca="false">ROUNDUP(I7/3,0)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="B8" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="L7" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="B8" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="22" t="n">
         <f aca="false">B8*120</f>
         <v>120</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="23" t="n">
         <f aca="false">D8/A8</f>
         <v>3</v>
       </c>
-      <c r="F8" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" s="20" t="n">
+      <c r="F8" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="H8" s="21" t="n">
+      <c r="H8" s="25" t="n">
         <f aca="false">A8*G8</f>
         <v>60</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="26" t="n">
         <f aca="false">A8^2*(G8/1000)</f>
         <v>2.4</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="22" t="n">
         <f aca="false">ROUNDUP(I8/3,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="B9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="22" t="n">
         <f aca="false">B9*120</f>
         <v>120</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="23" t="n">
         <f aca="false">D9/A9</f>
         <v>2.4</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="20" t="n">
+      <c r="F9" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="21" t="n">
+      <c r="H9" s="25" t="n">
         <f aca="false">A9*G9</f>
         <v>50</v>
       </c>
-      <c r="I9" s="22" t="n">
+      <c r="I9" s="26" t="n">
         <f aca="false">A9^2*(G9/1000)</f>
         <v>2.5</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="22" t="n">
         <f aca="false">ROUNDUP(I9/3,0)</f>
         <v>1</v>
       </c>
-      <c r="K9" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="M9" s="6" t="s">
+      <c r="K9" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="18" t="n">
+      <c r="C10" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="22" t="n">
         <f aca="false">B10*120</f>
         <v>240</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="23" t="n">
         <f aca="false">D10/A10</f>
         <v>3</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="20" t="n">
+      <c r="F10" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="H10" s="21" t="n">
+      <c r="H10" s="25" t="n">
         <f aca="false">A10*G10</f>
         <v>40</v>
       </c>
-      <c r="I10" s="22" t="n">
+      <c r="I10" s="26" t="n">
         <f aca="false">A10^2*(G10/1000)</f>
         <v>3.2</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J10" s="22" t="n">
         <f aca="false">ROUNDUP(I10/3,0)</f>
         <v>2</v>
       </c>
-      <c r="K10" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="M10" s="6" t="s">
+      <c r="K10" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="n">
+      <c r="A11" s="20" t="n">
         <v>120</v>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="18" t="n">
+      <c r="C11" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="22" t="n">
         <f aca="false">B11*120</f>
         <v>360</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="23" t="n">
         <f aca="false">D11/A11</f>
         <v>3</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="20" t="n">
+      <c r="F11" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="H11" s="21" t="n">
+      <c r="H11" s="25" t="n">
         <f aca="false">A11*G11</f>
         <v>60</v>
       </c>
-      <c r="I11" s="22" t="n">
+      <c r="I11" s="26" t="n">
         <f aca="false">A11^2*(G11/1000)</f>
         <v>7.2</v>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J11" s="22" t="n">
         <f aca="false">ROUNDUP(I11/3,0)</f>
         <v>3</v>
       </c>
-      <c r="K11" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="M11" s="6" t="s">
+      <c r="K11" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
+      <c r="A13" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2037,274 +2288,570 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>42</v>
+      <c r="B4" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="F5" s="8" t="s">
+      <c r="A5" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="A6" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="F7" s="7" t="s">
+      <c r="A7" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="A8" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="A9" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" s="8" t="s">
+      <c r="A10" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="F11" s="6" t="s">
+      <c r="A11" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="F12" s="6" t="s">
+      <c r="A12" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="F13" s="6" t="s">
+      <c r="A13" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14" s="6" t="s">
+      <c r="A14" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15" s="6" t="s">
+      <c r="A15" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2323,119 +2870,119 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>42</v>
+      <c r="A4" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="F5" s="8" t="s">
+      <c r="A5" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="A6" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="A7" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2454,157 +3001,157 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="B5" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="G6" s="6" t="s">
+      <c r="A6" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="A7" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="G8" s="6" t="s">
+      <c r="A8" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>7</v>
       </c>
     </row>

--- a/docs/decision-matrix.xlsx
+++ b/docs/decision-matrix.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Control" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="EMI Hardening" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Wire Egress" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Form Factor" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -930,6 +931,279 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="31" min="1" max="1"/>
+    <col width="32" customWidth="1" style="31" min="2" max="2"/>
+    <col width="26" customWidth="1" style="31" min="3" max="3"/>
+    <col width="26" customWidth="1" style="31" min="4" max="4"/>
+    <col width="32" customWidth="1" style="31" min="5" max="5"/>
+    <col width="26" customWidth="1" style="31" min="6" max="6"/>
+    <col width="42" customWidth="1" style="31" min="7" max="7"/>
+    <col width="34" customWidth="1" style="31" min="8" max="8"/>
+    <col width="46" customWidth="1" style="31" min="9" max="9"/>
+    <col width="16" customWidth="1" style="31" min="10" max="10"/>
+    <col width="20" customWidth="1" style="31" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="60" t="inlineStr">
+        <is>
+          <t>Form Factor Decision Matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="61" t="inlineStr">
+        <is>
+          <t>Build axis: Form Factor (Flat / Faceted rigid-flex). Strip width and sagitta derive from each other; see the preamble.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="61" t="inlineStr">
+        <is>
+          <t>Width from radial depth</t>
+        </is>
+      </c>
+      <c r="B4" s="61" t="inlineStr">
+        <is>
+          <t>w = 2 * sqrt(2*R*s - s^2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="61" t="inlineStr">
+        <is>
+          <t>Radial depth from width</t>
+        </is>
+      </c>
+      <c r="B5" s="61" t="inlineStr">
+        <is>
+          <t>s = R - sqrt(R^2 - (w/2)^2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="61" t="inlineStr">
+        <is>
+          <t>Reference host bore radius R (mm)</t>
+        </is>
+      </c>
+      <c r="B6" s="61" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="61" t="inlineStr">
+        <is>
+          <t>Reference radial depth budget s (mm)</t>
+        </is>
+      </c>
+      <c r="B7" s="61" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="61" t="inlineStr">
+        <is>
+          <t>Resulting max strip width w (mm)</t>
+        </is>
+      </c>
+      <c r="B8" s="61" t="n">
+        <v>23.98</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="62" t="inlineStr">
+        <is>
+          <t>Form Factor</t>
+        </is>
+      </c>
+      <c r="B10" s="62" t="inlineStr">
+        <is>
+          <t>Host Geometry</t>
+        </is>
+      </c>
+      <c r="C10" s="62" t="inlineStr">
+        <is>
+          <t>Max Strip Width (mm)</t>
+        </is>
+      </c>
+      <c r="D10" s="62" t="inlineStr">
+        <is>
+          <t>Sagitta / Radial Depth (mm)</t>
+        </is>
+      </c>
+      <c r="E10" s="62" t="inlineStr">
+        <is>
+          <t>Max Board Width (mm)</t>
+        </is>
+      </c>
+      <c r="F10" s="62" t="inlineStr">
+        <is>
+          <t>Max Board Length (mm)</t>
+        </is>
+      </c>
+      <c r="G10" s="62" t="inlineStr">
+        <is>
+          <t>Component-Driven Dimension</t>
+        </is>
+      </c>
+      <c r="H10" s="62" t="inlineStr">
+        <is>
+          <t>Facet Interconnect</t>
+        </is>
+      </c>
+      <c r="I10" s="62" t="inlineStr">
+        <is>
+          <t>Workflow Steps</t>
+        </is>
+      </c>
+      <c r="J10" s="62" t="inlineStr">
+        <is>
+          <t>REFERENCES.md Tags</t>
+        </is>
+      </c>
+      <c r="K10" s="62" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="63" t="inlineStr">
+        <is>
+          <t>Flat (default)</t>
+        </is>
+      </c>
+      <c r="B11" s="63" t="inlineStr">
+        <is>
+          <t>Planar mounting, no host curvature. Sagitta does not apply.</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>n/a -- one rigid panel</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E11" s="63" t="inlineStr">
+        <is>
+          <t>No host limit. The LOWER bound of 31.86 mm is set by [9] Table 6 creepage via docs/tools/isolation_envelope.py, not by any enclosure.</t>
+        </is>
+      </c>
+      <c r="F11" s="63" t="inlineStr">
+        <is>
+          <t>Driven by components.</t>
+        </is>
+      </c>
+      <c r="G11" s="63" t="inlineStr">
+        <is>
+          <t>Length. Width is pinned at the creepage minimum, so the part count sets the length.</t>
+        </is>
+      </c>
+      <c r="H11" s="63" t="inlineStr">
+        <is>
+          <t>None -- a single rigid board.</t>
+        </is>
+      </c>
+      <c r="I11" s="63" t="inlineStr">
+        <is>
+          <t>Default; no extra step. Both existing builds are this form factor: builds/6s/50A/CAN_485_faraday/ at 32.00 x 66.10 mm and .../CAN_485_faraday_sameend/ at 32.00 x 76.10 mm.</t>
+        </is>
+      </c>
+      <c r="J11" s="63" t="inlineStr">
+        <is>
+          <t>[9]</t>
+        </is>
+      </c>
+      <c r="K11" s="63" t="inlineStr">
+        <is>
+          <t>Candidate (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="63" t="inlineStr">
+        <is>
+          <t>Faceted rigid-flex</t>
+        </is>
+      </c>
+      <c r="B12" s="63" t="inlineStr">
+        <is>
+          <t>Cylindrical bore of radius R. Each rigid facet is a flat chord; its sagitta is the radial depth it consumes from the annulus. At the reference R = 30.0 mm a 24.00 mm facet subtends 47.16 deg, so 4 facets cover 180 deg.</t>
+        </is>
+      </c>
+      <c r="C12" s="63" t="inlineStr">
+        <is>
+          <t>24.00 mm nominal at the reference geometry (23.98 mm exact for s = 2.5 mm, rounded down). Recompute per host: docs/tools/strip_width.py --radius R --depth s</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="inlineStr">
+        <is>
+          <t>2.505 mm at w = 24.00 mm, R = 30.0 mm. This is the depth the board steals from the annulus -- budget it against the bore contents, not against the skin alone.</t>
+        </is>
+      </c>
+      <c r="E12" s="63" t="inlineStr">
+        <is>
+          <t>Equals the strip width for a single-facet-wide board.</t>
+        </is>
+      </c>
+      <c r="F12" s="63" t="inlineStr">
+        <is>
+          <t>Driven by components; the sum of the facet lengths plus the flex hinges between them.</t>
+        </is>
+      </c>
+      <c r="G12" s="63" t="inlineStr">
+        <is>
+          <t>Length, and it grows faster than the width shrinks. At 24.00 mm on THIS design: isolation_envelope.py can no longer seat the control section between the isolated rows and stacks it in Y instead, +19.50 mm; and the FET bridge spans 26.96 mm across Q1-Q6 as a 3x2, so it does not fit the strip at all and must become 2x3, adding more. Estimated 24 x 105-115 mm -- a new layout sharing the BOM, NOT a variant of the flat board.</t>
+        </is>
+      </c>
+      <c r="H12" s="63" t="inlineStr">
+        <is>
+          <t>Flex hinge -- TBD -- requires primary-source verification (AGENTS.md Sec.1.3). No flex or rigid-flex standard is catalogued in REFERENCES.md; neither IPC-2223 (flex design) nor IPC-6013 (flex qualification) has been obtained. Bend radius, flex-zone layer count and copper limits cannot be stated until one is.</t>
+        </is>
+      </c>
+      <c r="I12" s="63" t="inlineStr">
+        <is>
+          <t>Acquire and cite a flex design standard FIRST (AGENTS.md Sec.2). Then: run strip_width.py for the actual host radius and depth budget; re-run isolation_envelope.py at the target width to price the length; re-lay the FET bridge to fit the strip; keep the whole 50 A power stage on ONE rigid facet -- flex copper is thin and polyimide is a poor thermal path, and conductor_sizing.py already requires 2 oz just for the phase pours; re-run conductor_sizing.py for the new geometry.</t>
+        </is>
+      </c>
+      <c r="J12" s="63" t="inlineStr">
+        <is>
+          <t>[9]</t>
+        </is>
+      </c>
+      <c r="K12" s="63" t="inlineStr">
+        <is>
+          <t>Open / unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="64" t="inlineStr">
+        <is>
+          <t>Note: Choose the dimension the enclosure actually constrains and let the components drive the other -- they are not independent. A board carries a fixed part list, so narrowing it does not shrink it, it lengthens it, usually by more than the width saved. Both figures in the 'Component-Driven Dimension' cells come from this repo's own tools (docs/tools/isolation_envelope.py and measurements of the Q1-Q6 placement), not from estimation. -- Curvature is NOT what blocks a narrow board on this design: creepage is. [9] Table 6 forces a 31.86 mm minimum width while the isolated transceivers sit either side of the control section, and no amount of bending changes that; only restacking the isolation section does. -- True curved rigid FR-4 does not exist: the laminate is pressed flat. 'Curved' means faceted, whether the facets are joined by flex hinges or are separate boards with an interconnect.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">

--- a/docs/decision-matrix.xlsx
+++ b/docs/decision-matrix.xlsx
@@ -937,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="31" min="1" max="1"/>
@@ -963,7 +963,7 @@
     <row r="2">
       <c r="A2" s="61" t="inlineStr">
         <is>
-          <t>Build axis: Form Factor (Flat / Faceted rigid-flex). Strip width and sagitta derive from each other; see the preamble.</t>
+          <t>Build axis: Form Factor (Flat / Faceted rigid-flex / Faceted separate boards). Strip width and sagitta derive from each other; see the preamble.</t>
         </is>
       </c>
     </row>
@@ -1192,10 +1192,67 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="64" t="inlineStr">
-        <is>
-          <t>Note: Choose the dimension the enclosure actually constrains and let the components drive the other -- they are not independent. A board carries a fixed part list, so narrowing it does not shrink it, it lengthens it, usually by more than the width saved. Both figures in the 'Component-Driven Dimension' cells come from this repo's own tools (docs/tools/isolation_envelope.py and measurements of the Q1-Q6 placement), not from estimation. -- Curvature is NOT what blocks a narrow board on this design: creepage is. [9] Table 6 forces a 31.86 mm minimum width while the isolated transceivers sit either side of the control section, and no amount of bending changes that; only restacking the isolation section does. -- True curved rigid FR-4 does not exist: the laminate is pressed flat. 'Curved' means faceted, whether the facets are joined by flex hinges or are separate boards with an interconnect.</t>
+    <row r="13">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>Faceted separate boards</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>Same chord geometry as rigid-flex -- each rigid panel is a flat chord of the bore -- but the panels are independent boards joined by an interconnect rather than by a flex hinge. NOTE: the panels meet AT the bore circle, the point of maximum radius, so a connector at the joint has no outward room and protrudes inward into the bore. Budget its height against the bore contents (TODO.md 16.3).</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>Identical to rigid-flex: 24.00 mm nominal at the reference geometry. docs/tools/hinge_placement.py chooses the CUT position exactly as it chooses a fold.</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>2.505 mm per panel, as rigid-flex, PLUS the interconnect height at the joint vertex.</t>
+        </is>
+      </c>
+      <c r="E13" s="63" t="inlineStr">
+        <is>
+          <t>Equals the strip width per panel.</t>
+        </is>
+      </c>
+      <c r="F13" s="63" t="inlineStr">
+        <is>
+          <t>Driven by components, as rigid-flex.</t>
+        </is>
+      </c>
+      <c r="G13" s="63" t="inlineStr">
+        <is>
+          <t>Length -- AND the form factor should drive the functional partition. Faceting makes logic-vs-power placement a first-class layout decision: if the whole 50 A power stage sits on ONE panel the joint carries signals only, and either form factor works. If the cut splits the power stage the joint carries up to 50 A, which only separate boards can realistically do. On the current layout the power stage spans 26.96 mm in X and logic spans 28.74 mm, overlapping over 26.96 mm, so EVERY cut splits both -- the partition must be re-oriented along the cut axis.</t>
+        </is>
+      </c>
+      <c r="H13" s="63" t="inlineStr">
+        <is>
+          <t>Board-to-board connector, busbar, solder tab or wire link -- TBD -- requires primary-source verification (AGENTS.md Sec.1.3). No interconnect part has been selected. The decisive advantage over a flex hinge is that this joint CAN carry 50 A; flex copper is thin and conductor_sizing.py already requires 2 oz for the phase pours alone. The decisive disadvantage is a rigid joint in a vibration environment, where a flex hinge is compliant -- an engineering judgement here, no standard is cited for it.</t>
+        </is>
+      </c>
+      <c r="I13" s="63" t="inlineStr">
+        <is>
+          <t>NOT blocked by the flex-standard gate (16.2): standard rigid FR-4 on both panels, any fab, full copper weight throughout. Run hinge_placement.py --optimize for the cut, then: keep the whole power stage on one panel if the interconnect is to stay signal-only; keep any rigid shielding can wholly on one panel (SH1 is 22.75 mm and nearly fills a 23.98 mm facet by itself); and either give the isolated section its own panel or let the isolation barrier fall ON the cut, where the inter-panel gap supplies the separation instead of 7.5 mm of board surface.</t>
+        </is>
+      </c>
+      <c r="J13" s="63" t="inlineStr">
+        <is>
+          <t>[9], [19]</t>
+        </is>
+      </c>
+      <c r="K13" s="63" t="inlineStr">
+        <is>
+          <t>Open / unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="64" t="inlineStr">
+        <is>
+          <t>Note: Choose the dimension the enclosure actually constrains and let the components drive the other -- they are not independent. A board carries a fixed part list, so narrowing it does not shrink it, it lengthens it, usually by more than the width saved. Both figures in the 'Component-Driven Dimension' cells come from this repo's own tools (docs/tools/isolation_envelope.py and measurements of the Q1-Q6 placement), not from estimation. -- Curvature is NOT what blocks a narrow board on this design: creepage is. [9] Table 6 forces a 31.86 mm minimum width while the isolated transceivers sit either side of the control section, and no amount of bending changes that; only restacking the isolation section does. -- True curved rigid FR-4 does not exist: the laminate is pressed flat. 'Curved' means faceted, whether the facets are joined by flex hinges or are separate boards with an interconnect. -- CHOOSING BETWEEN THE TWO FACETED ROWS: run docs/tools/hinge_placement.py --optimize and read what crosses the cut. A signal-only joint favours rigid-flex (no connector, self-locating, compliant under vibration); a joint carrying Power-netclass conductors favours separate boards, because a flex hinge cannot realistically pass 50 A. Separate boards also avoid the flex-standard acquisition gate (16.2) entirely. The tool also checks the two constraints faceting imposes on placement: a rigid shielding can may not straddle a joint, and a panel holding both sides of an isolation barrier must still meet the 31.86 mm width isolation_envelope.py derives from [9] Table 6.</t>
         </is>
       </c>
     </row>
